--- a/8306.T_settings.xlsx
+++ b/8306.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -482,42 +497,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="F2" t="n">
-        <v>21.30419938545579</v>
+        <v>59.87377431014098</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>21.30%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>213,042円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>67日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.742110894383811</v>
+      </c>
+      <c r="I2" t="n">
+        <v>598737.7431014099</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1598737.74310141</v>
+      </c>
+      <c r="K2" t="n">
+        <v>41527.73434486792</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11.5625</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.956296353461906</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -525,11 +541,11 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,33 +554,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="F3" t="n">
-        <v>21.30419938545579</v>
+        <v>54.12538806164945</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>21.30%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>213,042円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>67日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.38283675385309</v>
+      </c>
+      <c r="I3" t="n">
+        <v>541253.8806164945</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1541253.880616494</v>
+      </c>
+      <c r="K3" t="n">
+        <v>39765.59500076633</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8.9375</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.120659770531216</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -581,37 +598,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="F4" t="n">
-        <v>21.30419938545579</v>
+        <v>48.92569610450645</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>21.30%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>213,042円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>67日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.718094228028136</v>
+      </c>
+      <c r="I4" t="n">
+        <v>489256.9610450645</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1489256.961045064</v>
+      </c>
+      <c r="K4" t="n">
+        <v>44393.3646182239</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.44444444444444</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11.10308433326963</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -619,11 +637,11 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -632,33 +650,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>56.25</v>
       </c>
       <c r="F5" t="n">
-        <v>21.30419938545579</v>
+        <v>48.17973577496772</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>21.30%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>213,042円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>67日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.011233485935483</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481797.3577496773</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1481797.357749677</v>
+      </c>
+      <c r="K5" t="n">
+        <v>39265.36545700914</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10.375</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.120659770531216</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -670,42 +689,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="F6" t="n">
-        <v>21.30419938545579</v>
+        <v>43.38645464541286</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>21.30%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>213,042円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>67日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.552144390906639</v>
+      </c>
+      <c r="I6" t="n">
+        <v>433864.5464541286</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1433864.546454129</v>
+      </c>
+      <c r="K6" t="n">
+        <v>41153.1020742237</v>
+      </c>
+      <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11.34373440255079</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -726,33 +746,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>56.25</v>
       </c>
       <c r="F7" t="n">
-        <v>21.30419938545579</v>
+        <v>38.90283621597493</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>21.30%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>213,042円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>67日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.431427263498433</v>
+      </c>
+      <c r="I7" t="n">
+        <v>389028.3621597493</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1389028.362159749</v>
+      </c>
+      <c r="K7" t="n">
+        <v>38787.19213136237</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13.4375</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11.34373440255081</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -760,46 +781,47 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>56.25</v>
       </c>
       <c r="F8" t="n">
-        <v>18.63105175292154</v>
+        <v>37.4697528374457</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>18.63%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>186,311円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.341859552340356</v>
+      </c>
+      <c r="I8" t="n">
+        <v>374697.528374457</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1374697.528374457</v>
+      </c>
+      <c r="K8" t="n">
+        <v>38179.185043681</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10.1875</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11.10308433326964</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -807,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -816,37 +838,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="F9" t="n">
-        <v>18.63105175292154</v>
+        <v>35.38353195392245</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>18.63%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>186,311円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.081384232583674</v>
+      </c>
+      <c r="I9" t="n">
+        <v>353835.3195392245</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1353835.319539224</v>
+      </c>
+      <c r="K9" t="n">
+        <v>39804.89355332521</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13.82352941176471</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11.78676778587216</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -854,46 +877,47 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="F10" t="n">
-        <v>18.63105175292154</v>
+        <v>34.18509498770484</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>18.63%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>186,311円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.441792499121774</v>
+      </c>
+      <c r="I10" t="n">
+        <v>341850.9498770484</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1341850.949877048</v>
+      </c>
+      <c r="K10" t="n">
+        <v>32777.88551793098</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.42857142857143</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.09171274509316</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -905,7 +929,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -914,33 +938,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="F11" t="n">
-        <v>18.57289177193582</v>
+        <v>32.2584779298523</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.30417699498945</v>
+      </c>
+      <c r="I11" t="n">
+        <v>322584.779298523</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1322584.779298523</v>
+      </c>
+      <c r="K11" t="n">
+        <v>31799.12684932547</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7.276081173384038</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -952,42 +977,43 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>46.875</v>
       </c>
       <c r="F12" t="n">
-        <v>18.57289177193582</v>
+        <v>31.57833101074081</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9868228440856502</v>
+      </c>
+      <c r="I12" t="n">
+        <v>315783.3101074081</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1315783.310107408</v>
+      </c>
+      <c r="K12" t="n">
+        <v>67656.77170900279</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.15625</v>
+      </c>
+      <c r="M12" t="n">
+        <v>27.17063168083949</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -995,7 +1021,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1004,37 +1030,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>18.57289177193582</v>
+        <v>31.15016067480063</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.946885042175039</v>
+      </c>
+      <c r="I13" t="n">
+        <v>311501.6067480063</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1311501.606748006</v>
+      </c>
+      <c r="K13" t="n">
+        <v>37590.23712138651</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12.1875</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11.78676778587216</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1051,37 +1078,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>18.57289177193582</v>
+        <v>30.24057877646196</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.008019292548732</v>
+      </c>
+      <c r="I14" t="n">
+        <v>302405.7877646196</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1302405.78776462</v>
+      </c>
+      <c r="K14" t="n">
+        <v>60961.56502888039</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>24.72721195005946</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1089,7 +1117,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1098,37 +1126,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>46.875</v>
       </c>
       <c r="F15" t="n">
-        <v>18.57289177193582</v>
+        <v>28.0710815638949</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8772212988717155</v>
+      </c>
+      <c r="I15" t="n">
+        <v>280710.8156389489</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1280710.815638949</v>
+      </c>
+      <c r="K15" t="n">
+        <v>66978.05177646714</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11.5625</v>
+      </c>
+      <c r="M15" t="n">
+        <v>28.08278339120081</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1140,7 +1169,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1149,33 +1178,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>18.57289177193582</v>
+        <v>28.01650111796235</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.001178651283025</v>
+      </c>
+      <c r="I16" t="n">
+        <v>280165.0111796234</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1280165.011179623</v>
+      </c>
+      <c r="K16" t="n">
+        <v>32202.71184421079</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12.71428571428571</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6.813937375463008</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1213,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1192,37 +1222,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="F17" t="n">
-        <v>18.57289177193582</v>
+        <v>26.76898741060593</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8922995803535311</v>
+      </c>
+      <c r="I17" t="n">
+        <v>267689.8741060593</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1267689.874106059</v>
+      </c>
+      <c r="K17" t="n">
+        <v>60316.77762903649</v>
+      </c>
+      <c r="L17" t="n">
+        <v>12.33333333333333</v>
+      </c>
+      <c r="M17" t="n">
+        <v>25.66996628046261</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1234,7 +1265,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1243,33 +1274,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>18.57289177193582</v>
+        <v>26.1784521546027</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.869889439614478</v>
+      </c>
+      <c r="I18" t="n">
+        <v>261784.5215460269</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1261784.521546027</v>
+      </c>
+      <c r="K18" t="n">
+        <v>31249.36976938966</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7.276081173384038</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1281,42 +1313,43 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="F19" t="n">
-        <v>18.57289177193582</v>
+        <v>26.04199910505286</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9300713966090307</v>
+      </c>
+      <c r="I19" t="n">
+        <v>260419.9910505286</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1260419.991050529</v>
+      </c>
+      <c r="K19" t="n">
+        <v>62102.29129107497</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="M19" t="n">
+        <v>25.9771904607237</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1333,37 +1366,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="F20" t="n">
-        <v>18.57289177193582</v>
+        <v>25.08647895800122</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7378376164118006</v>
+      </c>
+      <c r="I20" t="n">
+        <v>250864.7895800122</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1250864.789580012</v>
+      </c>
+      <c r="K20" t="n">
+        <v>72691.54196820447</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9.911764705882353</v>
+      </c>
+      <c r="M20" t="n">
+        <v>26.57293583518895</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1371,7 +1405,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1384,33 +1418,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>18.57289177193582</v>
+        <v>24.49292355068792</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.749494539334851</v>
+      </c>
+      <c r="I21" t="n">
+        <v>244929.2355068792</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1244929.235506879</v>
+      </c>
+      <c r="K21" t="n">
+        <v>31460.79761419038</v>
+      </c>
+      <c r="L21" t="n">
+        <v>13.07142857142857</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.524490599910509</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1418,46 +1453,47 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>45.16129032258064</v>
       </c>
       <c r="F22" t="n">
-        <v>18.57289177193582</v>
+        <v>23.72457782079498</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>185,729円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>63日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.7653089619611284</v>
+      </c>
+      <c r="I22" t="n">
+        <v>237245.7782079498</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1237245.77820795</v>
+      </c>
+      <c r="K22" t="n">
+        <v>64238.52542062043</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11.25806451612903</v>
+      </c>
+      <c r="M22" t="n">
+        <v>31.42217250767574</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1465,11 +1501,11 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1478,33 +1514,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="F23" t="n">
-        <v>15.95993322203673</v>
+        <v>23.60665302938903</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>15.96%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>159,599円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>60日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7153531221026977</v>
+      </c>
+      <c r="I23" t="n">
+        <v>236066.5302938903</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1236066.53029389</v>
+      </c>
+      <c r="K23" t="n">
+        <v>66099.64383809247</v>
+      </c>
+      <c r="L23" t="n">
+        <v>12</v>
+      </c>
+      <c r="M23" t="n">
+        <v>27.37187107890151</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1512,46 +1549,47 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>15.95993322203673</v>
+        <v>22.70546578485582</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>15.96%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>159,599円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>60日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.621818984632558</v>
+      </c>
+      <c r="I24" t="n">
+        <v>227054.6578485582</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1227054.657848558</v>
+      </c>
+      <c r="K24" t="n">
+        <v>30563.08665587718</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13.35714285714286</v>
+      </c>
+      <c r="M24" t="n">
+        <v>8.142078090013634</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1559,11 +1597,11 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1572,33 +1610,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>45.16129032258064</v>
       </c>
       <c r="F25" t="n">
-        <v>15.95993322203673</v>
+        <v>20.42667189821715</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>15.96%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>159,599円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>60日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6589248999424887</v>
+      </c>
+      <c r="I25" t="n">
+        <v>204266.7189821715</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1204266.718982172</v>
+      </c>
+      <c r="K25" t="n">
+        <v>63623.56494365155</v>
+      </c>
+      <c r="L25" t="n">
+        <v>11.67741935483871</v>
+      </c>
+      <c r="M25" t="n">
+        <v>32.28107577820607</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1606,11 +1645,11 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1619,33 +1658,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="F26" t="n">
-        <v>15.95993322203673</v>
+        <v>20.31189041814702</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>15.96%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>159,599円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>60日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6155118308529399</v>
+      </c>
+      <c r="I26" t="n">
+        <v>203118.9041814702</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1203118.90418147</v>
+      </c>
+      <c r="K26" t="n">
+        <v>65461.90412921367</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12.39393939393939</v>
+      </c>
+      <c r="M26" t="n">
+        <v>28.28150236562919</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1657,7 +1697,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1666,33 +1706,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>40.625</v>
       </c>
       <c r="F27" t="n">
-        <v>15.95993322203673</v>
+        <v>18.70682361831605</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>15.96%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>159,599円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>60日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5845882380723765</v>
+      </c>
+      <c r="I27" t="n">
+        <v>187068.2361831605</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1187068.23618316</v>
+      </c>
+      <c r="K27" t="n">
+        <v>64218.0371297751</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10.625</v>
+      </c>
+      <c r="M27" t="n">
+        <v>27.24028395028997</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1700,11 +1741,11 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1713,33 +1754,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>42.42424242424242</v>
       </c>
       <c r="F28" t="n">
-        <v>15.95993322203673</v>
+        <v>17.62021665182183</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>15.96%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>159,599円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>60日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5339459591461162</v>
+      </c>
+      <c r="I28" t="n">
+        <v>176202.1665182183</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1176202.166518218</v>
+      </c>
+      <c r="K28" t="n">
+        <v>68806.5001747355</v>
+      </c>
+      <c r="L28" t="n">
+        <v>9.969696969696969</v>
+      </c>
+      <c r="M28" t="n">
+        <v>30.85936819477437</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1747,11 +1789,11 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1760,33 +1802,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F29" t="n">
-        <v>12.1173871883875</v>
+        <v>17.50811006994383</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>12.12%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>121,174円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>47日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5002317162841093</v>
+      </c>
+      <c r="I29" t="n">
+        <v>175081.1006994382</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1175081.100699438</v>
+      </c>
+      <c r="K29" t="n">
+        <v>70831.52798490437</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10.74285714285714</v>
+      </c>
+      <c r="M29" t="n">
+        <v>26.77582676415089</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1794,11 +1837,11 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1807,33 +1850,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F30" t="n">
-        <v>11.62425384857053</v>
+        <v>16.55007946241924</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>11.62%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>116,243円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>41日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5910742665149729</v>
+      </c>
+      <c r="I30" t="n">
+        <v>165500.7946241924</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1165500.794624192</v>
+      </c>
+      <c r="K30" t="n">
+        <v>59024.75572479467</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9.357142857142858</v>
+      </c>
+      <c r="M30" t="n">
+        <v>30.08178128799766</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1841,46 +1885,47 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F31" t="n">
-        <v>9.592931524140107</v>
+        <v>13.44341137669126</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>9.59%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>95,929円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>43日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4801218348818307</v>
+      </c>
+      <c r="I31" t="n">
+        <v>134434.1137669126</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1134434.113766913</v>
+      </c>
+      <c r="K31" t="n">
+        <v>58337.63986865056</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9.821428571428571</v>
+      </c>
+      <c r="M31" t="n">
+        <v>30.95747229363816</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1888,46 +1933,47 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F32" t="n">
-        <v>9.592931524140107</v>
+        <v>6.678532226397167</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>9.59%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>95,929円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>43日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2385190080856131</v>
+      </c>
+      <c r="I32" t="n">
+        <v>66785.32226397167</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1066785.322263972</v>
+      </c>
+      <c r="K32" t="n">
+        <v>56623.50318413318</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>34.931312811978</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,7 +1981,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1944,37 +1990,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100</v>
+        <v>38.70967741935484</v>
       </c>
       <c r="F33" t="n">
-        <v>9.110901665095822</v>
+        <v>3.482734412665514</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>9.11%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>91,109円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>37日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1123462713763069</v>
+      </c>
+      <c r="I33" t="n">
+        <v>34827.34412665514</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1034827.344126655</v>
+      </c>
+      <c r="K33" t="n">
+        <v>55034.59564065361</v>
+      </c>
+      <c r="L33" t="n">
+        <v>12</v>
+      </c>
+      <c r="M33" t="n">
+        <v>32.20717873358061</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,7 +2029,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1991,37 +2038,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
+        <v>38.70967741935484</v>
       </c>
       <c r="F34" t="n">
-        <v>9.110901665095822</v>
+        <v>0.7243792926472262</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>9.11%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>91,109円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>37日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.02336707395636214</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7243.792926472262</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1007243.792926472</v>
+      </c>
+      <c r="K34" t="n">
+        <v>54465.62760160865</v>
+      </c>
+      <c r="L34" t="n">
+        <v>12.41935483870968</v>
+      </c>
+      <c r="M34" t="n">
+        <v>33.05625019054274</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2029,46 +2077,47 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="F35" t="n">
-        <v>8.389261744966444</v>
+        <v>-0.2618697552753496</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>8.39%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>83,893円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>32日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.01047479021101399</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-2618.697552753496</v>
+      </c>
+      <c r="J35" t="n">
+        <v>997381.3024472465</v>
+      </c>
+      <c r="K35" t="n">
+        <v>46411.74670743827</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="M35" t="n">
+        <v>30.51011804255807</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2076,46 +2125,47 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="F36" t="n">
-        <v>5.948749237339841</v>
+        <v>-1.154327316729259</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>5.95%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>59,487円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>28日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.04122597559747353</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-11543.27316729259</v>
+      </c>
+      <c r="J36" t="n">
+        <v>988456.7268327074</v>
+      </c>
+      <c r="K36" t="n">
+        <v>52827.38811631487</v>
+      </c>
+      <c r="L36" t="n">
+        <v>10.17857142857143</v>
+      </c>
+      <c r="M36" t="n">
+        <v>34.93131281197799</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2127,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2136,33 +2186,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F37" t="n">
-        <v>5.948749237339841</v>
+        <v>-1.622879821638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>5.95%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>59,487円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>28日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.04917817641329337</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-16228.79821638681</v>
+      </c>
+      <c r="J37" t="n">
+        <v>983771.2017836132</v>
+      </c>
+      <c r="K37" t="n">
+        <v>58880.78614473325</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="M37" t="n">
+        <v>31.65078300280713</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2170,11 +2221,11 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2183,33 +2234,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="F38" t="n">
-        <v>3.105049332559489</v>
+        <v>-4.271218643738259</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>3.11%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>31,050円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.1642776401437792</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-42712.1864373826</v>
+      </c>
+      <c r="J38" t="n">
+        <v>957287.8135626174</v>
+      </c>
+      <c r="K38" t="n">
+        <v>47714.19207922939</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9.423076923076923</v>
+      </c>
+      <c r="M38" t="n">
+        <v>30.99121406496133</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2221,7 +2273,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2230,33 +2282,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7835171213000581</v>
+        <v>-4.544233371829346</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>7,835円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>10日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.1817693348731738</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-45442.33371829346</v>
+      </c>
+      <c r="J39" t="n">
+        <v>954557.6662817065</v>
+      </c>
+      <c r="K39" t="n">
+        <v>44932.06087040354</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="M39" t="n">
+        <v>32.06555669781145</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2264,11 +2317,11 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2277,33 +2330,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7835171213000581</v>
+        <v>-6.727014596117032</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7,835円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>10日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.2491486887450753</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-67270.14596117032</v>
+      </c>
+      <c r="J40" t="n">
+        <v>932729.8540388297</v>
+      </c>
+      <c r="K40" t="n">
+        <v>49483.57190600705</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11.44444444444444</v>
+      </c>
+      <c r="M40" t="n">
+        <v>39.01207413000407</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2311,46 +2365,47 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-7.088627894340677</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.2835451157736271</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-70886.27894340677</v>
+      </c>
+      <c r="J41" t="n">
+        <v>929113.7210565932</v>
+      </c>
+      <c r="K41" t="n">
+        <v>44404.20937707005</v>
+      </c>
+      <c r="L41" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M41" t="n">
+        <v>32.91640190051838</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2362,42 +2417,43 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-8.381436564720341</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.3223629447969362</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-83814.36564720341</v>
+      </c>
+      <c r="J42" t="n">
+        <v>916185.6343527966</v>
+      </c>
+      <c r="K42" t="n">
+        <v>46179.1633460391</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.11538461538461</v>
+      </c>
+      <c r="M42" t="n">
+        <v>32.53588402513194</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2405,46 +2461,47 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-9.213226603447682</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.3412306149425067</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-92132.26603447681</v>
+      </c>
+      <c r="J43" t="n">
+        <v>907867.7339655232</v>
+      </c>
+      <c r="K43" t="n">
+        <v>48943.57790762297</v>
+      </c>
+      <c r="L43" t="n">
+        <v>11.92592592592593</v>
+      </c>
+      <c r="M43" t="n">
+        <v>39.77591764777173</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2452,46 +2509,47 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-9.301108124243877</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.3321824330087099</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-93011.08124243875</v>
+      </c>
+      <c r="J44" t="n">
+        <v>906988.9187575612</v>
+      </c>
+      <c r="K44" t="n">
+        <v>50156.5980749895</v>
+      </c>
+      <c r="L44" t="n">
+        <v>10.92857142857143</v>
+      </c>
+      <c r="M44" t="n">
+        <v>39.01207413000407</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2508,37 +2566,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-10.82354958941716</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.416290368823737</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-108235.4958941716</v>
+      </c>
+      <c r="J45" t="n">
+        <v>891764.5041058284</v>
+      </c>
+      <c r="K45" t="n">
+        <v>45617.73772006088</v>
+      </c>
+      <c r="L45" t="n">
+        <v>10.61538461538461</v>
+      </c>
+      <c r="M45" t="n">
+        <v>33.38083861137537</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2550,42 +2609,43 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-11.71870710058915</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.4185252535924698</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-117187.0710058915</v>
+      </c>
+      <c r="J46" t="n">
+        <v>882812.9289941085</v>
+      </c>
+      <c r="K46" t="n">
+        <v>49631.50651647533</v>
+      </c>
+      <c r="L46" t="n">
+        <v>11.39285714285714</v>
+      </c>
+      <c r="M46" t="n">
+        <v>39.77591764777175</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/8306.T_settings.xlsx
+++ b/8306.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>62.5</v>
       </c>
       <c r="F2" t="n">
-        <v>59.87377431014098</v>
+        <v>59.87371606579844</v>
       </c>
       <c r="G2" t="n">
         <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>3.742110894383811</v>
+        <v>3.742107254112403</v>
       </c>
       <c r="I2" t="n">
-        <v>598737.7431014099</v>
+        <v>598737.1606579844</v>
       </c>
       <c r="J2" t="n">
-        <v>1598737.74310141</v>
+        <v>1598737.160657984</v>
       </c>
       <c r="K2" t="n">
-        <v>41527.73434486792</v>
+        <v>41527.72261851742</v>
       </c>
       <c r="L2" t="n">
         <v>11.5625</v>
       </c>
       <c r="M2" t="n">
-        <v>6.956296353461906</v>
+        <v>6.956316121209463</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,28 +557,28 @@
         <v>62.5</v>
       </c>
       <c r="F3" t="n">
-        <v>54.12538806164945</v>
+        <v>54.12534530822444</v>
       </c>
       <c r="G3" t="n">
         <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>3.38283675385309</v>
+        <v>3.382834081764027</v>
       </c>
       <c r="I3" t="n">
-        <v>541253.8806164945</v>
+        <v>541253.4530822444</v>
       </c>
       <c r="J3" t="n">
-        <v>1541253.880616494</v>
+        <v>1541253.453082244</v>
       </c>
       <c r="K3" t="n">
-        <v>39765.59500076633</v>
+        <v>39765.58654016149</v>
       </c>
       <c r="L3" t="n">
         <v>8.9375</v>
       </c>
       <c r="M3" t="n">
-        <v>9.120659770531216</v>
+        <v>9.120678927465647</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -605,28 +605,28 @@
         <v>61.11111111111111</v>
       </c>
       <c r="F4" t="n">
-        <v>48.92569610450645</v>
+        <v>48.92563003618191</v>
       </c>
       <c r="G4" t="n">
         <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>2.718094228028136</v>
+        <v>2.718090557565662</v>
       </c>
       <c r="I4" t="n">
-        <v>489256.9610450645</v>
+        <v>489256.3003618191</v>
       </c>
       <c r="J4" t="n">
-        <v>1489256.961045064</v>
+        <v>1489256.300361819</v>
       </c>
       <c r="K4" t="n">
-        <v>44393.3646182239</v>
+        <v>44393.34941996225</v>
       </c>
       <c r="L4" t="n">
         <v>10.44444444444444</v>
       </c>
       <c r="M4" t="n">
-        <v>11.10308433326963</v>
+        <v>11.10310307231836</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>56.25</v>
       </c>
       <c r="F5" t="n">
-        <v>48.17973577496772</v>
+        <v>48.17969467082971</v>
       </c>
       <c r="G5" t="n">
         <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>3.011233485935483</v>
+        <v>3.011230916926857</v>
       </c>
       <c r="I5" t="n">
-        <v>481797.3577496773</v>
+        <v>481796.9467082971</v>
       </c>
       <c r="J5" t="n">
-        <v>1481797.357749677</v>
+        <v>1481796.946708297</v>
       </c>
       <c r="K5" t="n">
-        <v>39265.36545700914</v>
+        <v>39265.35713516485</v>
       </c>
       <c r="L5" t="n">
         <v>10.375</v>
       </c>
       <c r="M5" t="n">
-        <v>9.120659770531216</v>
+        <v>9.120678927465647</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>58.82352941176471</v>
       </c>
       <c r="F6" t="n">
-        <v>43.38645464541286</v>
+        <v>43.38640406988133</v>
       </c>
       <c r="G6" t="n">
         <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>2.552144390906639</v>
+        <v>2.552141415875372</v>
       </c>
       <c r="I6" t="n">
-        <v>433864.5464541286</v>
+        <v>433864.0406988133</v>
       </c>
       <c r="J6" t="n">
-        <v>1433864.546454129</v>
+        <v>1433864.040698813</v>
       </c>
       <c r="K6" t="n">
-        <v>41153.1020742237</v>
+        <v>41153.09133966229</v>
       </c>
       <c r="L6" t="n">
         <v>15</v>
       </c>
       <c r="M6" t="n">
-        <v>11.34373440255079</v>
+        <v>11.34375323815826</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>56.25</v>
       </c>
       <c r="F7" t="n">
-        <v>38.90283621597493</v>
+        <v>38.90277572128261</v>
       </c>
       <c r="G7" t="n">
         <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>2.431427263498433</v>
+        <v>2.431423482580163</v>
       </c>
       <c r="I7" t="n">
-        <v>389028.3621597493</v>
+        <v>389027.7572128261</v>
       </c>
       <c r="J7" t="n">
-        <v>1389028.362159749</v>
+        <v>1389027.757212826</v>
       </c>
       <c r="K7" t="n">
-        <v>38787.19213136237</v>
+        <v>38787.17949960093</v>
       </c>
       <c r="L7" t="n">
         <v>13.4375</v>
       </c>
       <c r="M7" t="n">
-        <v>11.34373440255081</v>
+        <v>11.34375323815825</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>56.25</v>
       </c>
       <c r="F8" t="n">
-        <v>37.4697528374457</v>
+        <v>37.46970491586229</v>
       </c>
       <c r="G8" t="n">
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>2.341859552340356</v>
+        <v>2.341856557241393</v>
       </c>
       <c r="I8" t="n">
-        <v>374697.528374457</v>
+        <v>374697.049158623</v>
       </c>
       <c r="J8" t="n">
-        <v>1374697.528374457</v>
+        <v>1374697.049158623</v>
       </c>
       <c r="K8" t="n">
-        <v>38179.185043681</v>
+        <v>38179.17478681985</v>
       </c>
       <c r="L8" t="n">
         <v>10.1875</v>
       </c>
       <c r="M8" t="n">
-        <v>11.10308433326964</v>
+        <v>11.10310307231837</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>52.94117647058824</v>
       </c>
       <c r="F9" t="n">
-        <v>35.38353195392245</v>
+        <v>35.38349596883685</v>
       </c>
       <c r="G9" t="n">
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>2.081384232583674</v>
+        <v>2.081382115813932</v>
       </c>
       <c r="I9" t="n">
-        <v>353835.3195392245</v>
+        <v>353834.9596883685</v>
       </c>
       <c r="J9" t="n">
-        <v>1353835.319539224</v>
+        <v>1353834.959688368</v>
       </c>
       <c r="K9" t="n">
-        <v>39804.89355332521</v>
+        <v>39804.88556600332</v>
       </c>
       <c r="L9" t="n">
         <v>13.82352941176471</v>
       </c>
       <c r="M9" t="n">
-        <v>11.78676778587216</v>
+        <v>11.78678638080362</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -893,28 +893,28 @@
         <v>57.14285714285714</v>
       </c>
       <c r="F10" t="n">
-        <v>34.18509498770484</v>
+        <v>34.1850630964892</v>
       </c>
       <c r="G10" t="n">
         <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>2.441792499121774</v>
+        <v>2.4417902211778</v>
       </c>
       <c r="I10" t="n">
-        <v>341850.9498770484</v>
+        <v>341850.630964892</v>
       </c>
       <c r="J10" t="n">
-        <v>1341850.949877048</v>
+        <v>1341850.630964892</v>
       </c>
       <c r="K10" t="n">
-        <v>32777.88551793098</v>
+        <v>32777.87792357706</v>
       </c>
       <c r="L10" t="n">
         <v>10.42857142857143</v>
       </c>
       <c r="M10" t="n">
-        <v>6.09171274509316</v>
+        <v>6.091704671334564</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>57.14285714285714</v>
       </c>
       <c r="F11" t="n">
-        <v>32.2584779298523</v>
+        <v>32.25839648464306</v>
       </c>
       <c r="G11" t="n">
         <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>2.30417699498945</v>
+        <v>2.304171177474504</v>
       </c>
       <c r="I11" t="n">
-        <v>322584.779298523</v>
+        <v>322583.9648464306</v>
       </c>
       <c r="J11" t="n">
-        <v>1322584.779298523</v>
+        <v>1322583.964846431</v>
       </c>
       <c r="K11" t="n">
-        <v>31799.12684932547</v>
+        <v>31799.10956448398</v>
       </c>
       <c r="L11" t="n">
         <v>10.71428571428571</v>
       </c>
       <c r="M11" t="n">
-        <v>7.276081173384038</v>
+        <v>7.276117651245778</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -989,28 +989,28 @@
         <v>46.875</v>
       </c>
       <c r="F12" t="n">
-        <v>31.57833101074081</v>
+        <v>31.57839832748762</v>
       </c>
       <c r="G12" t="n">
         <v>32</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9868228440856502</v>
+        <v>0.986824947733988</v>
       </c>
       <c r="I12" t="n">
-        <v>315783.3101074081</v>
+        <v>315783.9832748761</v>
       </c>
       <c r="J12" t="n">
-        <v>1315783.310107408</v>
+        <v>1315783.983274876</v>
       </c>
       <c r="K12" t="n">
-        <v>67656.77170900279</v>
+        <v>67656.79257877896</v>
       </c>
       <c r="L12" t="n">
         <v>11.15625</v>
       </c>
       <c r="M12" t="n">
-        <v>27.17063168083949</v>
+        <v>27.17060594729972</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>31.15016067480063</v>
+        <v>31.15011495620997</v>
       </c>
       <c r="G13" t="n">
         <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>1.946885042175039</v>
+        <v>1.946882184763123</v>
       </c>
       <c r="I13" t="n">
-        <v>311501.6067480063</v>
+        <v>311501.1495620997</v>
       </c>
       <c r="J13" t="n">
-        <v>1311501.606748006</v>
+        <v>1311501.1495621</v>
       </c>
       <c r="K13" t="n">
-        <v>37590.23712138651</v>
+        <v>37590.22706996757</v>
       </c>
       <c r="L13" t="n">
         <v>12.1875</v>
       </c>
       <c r="M13" t="n">
-        <v>11.78676778587216</v>
+        <v>11.78678638080363</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>46.66666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>30.24057877646196</v>
+        <v>30.24060963749827</v>
       </c>
       <c r="G14" t="n">
         <v>30</v>
       </c>
       <c r="H14" t="n">
-        <v>1.008019292548732</v>
+        <v>1.008020321249943</v>
       </c>
       <c r="I14" t="n">
-        <v>302405.7877646196</v>
+        <v>302406.0963749827</v>
       </c>
       <c r="J14" t="n">
-        <v>1302405.78776462</v>
+        <v>1302406.096374983</v>
       </c>
       <c r="K14" t="n">
-        <v>60961.56502888039</v>
+        <v>60961.5679187255</v>
       </c>
       <c r="L14" t="n">
         <v>11.9</v>
       </c>
       <c r="M14" t="n">
-        <v>24.72721195005946</v>
+        <v>24.72718549054568</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>46.875</v>
       </c>
       <c r="F15" t="n">
-        <v>28.0710815638949</v>
+        <v>28.07113646595345</v>
       </c>
       <c r="G15" t="n">
         <v>32</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8772212988717155</v>
+        <v>0.8772230145610455</v>
       </c>
       <c r="I15" t="n">
-        <v>280710.8156389489</v>
+        <v>280711.3646595345</v>
       </c>
       <c r="J15" t="n">
-        <v>1280710.815638949</v>
+        <v>1280711.364659535</v>
       </c>
       <c r="K15" t="n">
-        <v>66978.05177646714</v>
+        <v>66978.06936641116</v>
       </c>
       <c r="L15" t="n">
         <v>11.5625</v>
       </c>
       <c r="M15" t="n">
-        <v>28.08278339120081</v>
+        <v>28.08276394372369</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>28.01650111796235</v>
+        <v>28.01647069281081</v>
       </c>
       <c r="G16" t="n">
         <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>2.001178651283025</v>
+        <v>2.001176478057915</v>
       </c>
       <c r="I16" t="n">
-        <v>280165.0111796234</v>
+        <v>280164.7069281081</v>
       </c>
       <c r="J16" t="n">
-        <v>1280165.011179623</v>
+        <v>1280164.706928108</v>
       </c>
       <c r="K16" t="n">
-        <v>32202.71184421079</v>
+        <v>32202.70438815813</v>
       </c>
       <c r="L16" t="n">
         <v>12.71428571428571</v>
       </c>
       <c r="M16" t="n">
-        <v>6.813937375463008</v>
+        <v>6.813929363797626</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1229,28 +1229,28 @@
         <v>46.66666666666666</v>
       </c>
       <c r="F17" t="n">
-        <v>26.76898741060593</v>
+        <v>26.7690069366686</v>
       </c>
       <c r="G17" t="n">
         <v>30</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8922995803535311</v>
+        <v>0.8923002312222867</v>
       </c>
       <c r="I17" t="n">
-        <v>267689.8741060593</v>
+        <v>267690.069366686</v>
       </c>
       <c r="J17" t="n">
-        <v>1267689.874106059</v>
+        <v>1267690.069366686</v>
       </c>
       <c r="K17" t="n">
-        <v>60316.77762903649</v>
+        <v>60316.77763400946</v>
       </c>
       <c r="L17" t="n">
         <v>12.33333333333333</v>
       </c>
       <c r="M17" t="n">
-        <v>25.66996628046261</v>
+        <v>25.6699463161878</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>26.1784521546027</v>
+        <v>26.17837445349346</v>
       </c>
       <c r="G18" t="n">
         <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>1.869889439614478</v>
+        <v>1.869883889535247</v>
       </c>
       <c r="I18" t="n">
-        <v>261784.5215460269</v>
+        <v>261783.7445349346</v>
       </c>
       <c r="J18" t="n">
-        <v>1261784.521546027</v>
+        <v>1261783.744534935</v>
       </c>
       <c r="K18" t="n">
-        <v>31249.36976938966</v>
+        <v>31249.35282315943</v>
       </c>
       <c r="L18" t="n">
         <v>13</v>
       </c>
       <c r="M18" t="n">
-        <v>7.276081173384038</v>
+        <v>7.276117651245778</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1325,28 +1325,28 @@
         <v>46.42857142857143</v>
       </c>
       <c r="F19" t="n">
-        <v>26.04199910505286</v>
+        <v>26.04198548748738</v>
       </c>
       <c r="G19" t="n">
         <v>28</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9300713966090307</v>
+        <v>0.9300709102674064</v>
       </c>
       <c r="I19" t="n">
-        <v>260419.9910505286</v>
+        <v>260419.8548748738</v>
       </c>
       <c r="J19" t="n">
-        <v>1260419.991050529</v>
+        <v>1260419.854874874</v>
       </c>
       <c r="K19" t="n">
-        <v>62102.29129107497</v>
+        <v>62102.28181397135</v>
       </c>
       <c r="L19" t="n">
         <v>8.928571428571429</v>
       </c>
       <c r="M19" t="n">
-        <v>25.9771904607237</v>
+        <v>25.97717910387065</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         <v>44.11764705882353</v>
       </c>
       <c r="F20" t="n">
-        <v>25.08647895800122</v>
+        <v>25.08659121353799</v>
       </c>
       <c r="G20" t="n">
         <v>34</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7378376164118006</v>
+        <v>0.7378409180452349</v>
       </c>
       <c r="I20" t="n">
-        <v>250864.7895800122</v>
+        <v>250865.9121353799</v>
       </c>
       <c r="J20" t="n">
-        <v>1250864.789580012</v>
+        <v>1250865.91213538</v>
       </c>
       <c r="K20" t="n">
-        <v>72691.54196820447</v>
+        <v>72691.58453997942</v>
       </c>
       <c r="L20" t="n">
         <v>9.911764705882353</v>
       </c>
       <c r="M20" t="n">
-        <v>26.57293583518895</v>
+        <v>26.57290101951372</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1421,28 +1421,28 @@
         <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>24.49292355068792</v>
+        <v>24.49289384414824</v>
       </c>
       <c r="G21" t="n">
         <v>14</v>
       </c>
       <c r="H21" t="n">
-        <v>1.749494539334851</v>
+        <v>1.74949241743916</v>
       </c>
       <c r="I21" t="n">
-        <v>244929.2355068792</v>
+        <v>244928.9384414824</v>
       </c>
       <c r="J21" t="n">
-        <v>1244929.235506879</v>
+        <v>1244928.938441482</v>
       </c>
       <c r="K21" t="n">
-        <v>31460.79761419038</v>
+        <v>31460.79030953017</v>
       </c>
       <c r="L21" t="n">
         <v>13.07142857142857</v>
       </c>
       <c r="M21" t="n">
-        <v>8.524490599910509</v>
+        <v>8.524482735309833</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1469,28 +1469,28 @@
         <v>45.16129032258064</v>
       </c>
       <c r="F22" t="n">
-        <v>23.72457782079498</v>
+        <v>23.72461918696731</v>
       </c>
       <c r="G22" t="n">
         <v>31</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7653089619611284</v>
+        <v>0.7653102963537841</v>
       </c>
       <c r="I22" t="n">
-        <v>237245.7782079498</v>
+        <v>237246.1918696731</v>
       </c>
       <c r="J22" t="n">
-        <v>1237245.77820795</v>
+        <v>1237246.191869673</v>
       </c>
       <c r="K22" t="n">
-        <v>64238.52542062043</v>
+        <v>64238.5360047479</v>
       </c>
       <c r="L22" t="n">
         <v>11.25806451612903</v>
       </c>
       <c r="M22" t="n">
-        <v>31.42217250767574</v>
+        <v>31.42215376069096</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1517,28 +1517,28 @@
         <v>45.45454545454545</v>
       </c>
       <c r="F23" t="n">
-        <v>23.60665302938903</v>
+        <v>23.60665976871744</v>
       </c>
       <c r="G23" t="n">
         <v>33</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7153531221026977</v>
+        <v>0.7153533263247708</v>
       </c>
       <c r="I23" t="n">
-        <v>236066.5302938903</v>
+        <v>236066.5976871743</v>
       </c>
       <c r="J23" t="n">
-        <v>1236066.53029389</v>
+        <v>1236066.597687174</v>
       </c>
       <c r="K23" t="n">
-        <v>66099.64383809247</v>
+        <v>66099.63839688202</v>
       </c>
       <c r="L23" t="n">
         <v>12</v>
       </c>
       <c r="M23" t="n">
-        <v>27.37187107890151</v>
+        <v>27.37185122469387</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -1565,28 +1565,28 @@
         <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>22.70546578485582</v>
+        <v>22.70539010530705</v>
       </c>
       <c r="G24" t="n">
         <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>1.621818984632558</v>
+        <v>1.621813578950504</v>
       </c>
       <c r="I24" t="n">
-        <v>227054.6578485582</v>
+        <v>227053.9010530706</v>
       </c>
       <c r="J24" t="n">
-        <v>1227054.657848558</v>
+        <v>1227053.901053071</v>
       </c>
       <c r="K24" t="n">
-        <v>30563.08665587718</v>
+        <v>30563.07008851082</v>
       </c>
       <c r="L24" t="n">
         <v>13.35714285714286</v>
       </c>
       <c r="M24" t="n">
-        <v>8.142078090013634</v>
+        <v>8.142114314863377</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,28 +1613,28 @@
         <v>45.16129032258064</v>
       </c>
       <c r="F25" t="n">
-        <v>20.42667189821715</v>
+        <v>20.42670217533712</v>
       </c>
       <c r="G25" t="n">
         <v>31</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6589248999424887</v>
+        <v>0.6589258766237782</v>
       </c>
       <c r="I25" t="n">
-        <v>204266.7189821715</v>
+        <v>204267.0217533712</v>
       </c>
       <c r="J25" t="n">
-        <v>1204266.718982172</v>
+        <v>1204267.021753371</v>
       </c>
       <c r="K25" t="n">
-        <v>63623.56494365155</v>
+        <v>63623.57270908629</v>
       </c>
       <c r="L25" t="n">
         <v>11.67741935483871</v>
       </c>
       <c r="M25" t="n">
-        <v>32.28107577820607</v>
+        <v>32.28106288163538</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -1661,28 +1661,28 @@
         <v>45.45454545454545</v>
       </c>
       <c r="F26" t="n">
-        <v>20.31189041814702</v>
+        <v>20.3118870009304</v>
       </c>
       <c r="G26" t="n">
         <v>33</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6155118308529399</v>
+        <v>0.6155117273009214</v>
       </c>
       <c r="I26" t="n">
-        <v>203118.9041814702</v>
+        <v>203118.870009304</v>
       </c>
       <c r="J26" t="n">
-        <v>1203118.90418147</v>
+        <v>1203118.870009304</v>
       </c>
       <c r="K26" t="n">
-        <v>65461.90412921367</v>
+        <v>65461.89589336907</v>
       </c>
       <c r="L26" t="n">
         <v>12.39393939393939</v>
       </c>
       <c r="M26" t="n">
-        <v>28.28150236562919</v>
+        <v>28.28148870736917</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1709,28 +1709,28 @@
         <v>40.625</v>
       </c>
       <c r="F27" t="n">
-        <v>18.70682361831605</v>
+        <v>18.70688826851281</v>
       </c>
       <c r="G27" t="n">
         <v>32</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5845882380723765</v>
+        <v>0.5845902583910254</v>
       </c>
       <c r="I27" t="n">
-        <v>187068.2361831605</v>
+        <v>187068.8826851281</v>
       </c>
       <c r="J27" t="n">
-        <v>1187068.23618316</v>
+        <v>1187068.882685128</v>
       </c>
       <c r="K27" t="n">
-        <v>64218.0371297751</v>
+        <v>64218.05506350842</v>
       </c>
       <c r="L27" t="n">
         <v>10.625</v>
       </c>
       <c r="M27" t="n">
-        <v>27.24028395028997</v>
+        <v>27.24025526979018</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>42.42424242424242</v>
       </c>
       <c r="F28" t="n">
-        <v>17.62021665182183</v>
+        <v>17.62030135654665</v>
       </c>
       <c r="G28" t="n">
         <v>33</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5339459591461162</v>
+        <v>0.5339485259559591</v>
       </c>
       <c r="I28" t="n">
-        <v>176202.1665182183</v>
+        <v>176203.0135654665</v>
       </c>
       <c r="J28" t="n">
-        <v>1176202.166518218</v>
+        <v>1176203.013565467</v>
       </c>
       <c r="K28" t="n">
-        <v>68806.5001747355</v>
+        <v>68806.52950685048</v>
       </c>
       <c r="L28" t="n">
         <v>9.969696969696969</v>
       </c>
       <c r="M28" t="n">
-        <v>30.85936819477437</v>
+        <v>30.85934094084897</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1805,28 +1805,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F29" t="n">
-        <v>17.50811006994383</v>
+        <v>17.50816181298972</v>
       </c>
       <c r="G29" t="n">
         <v>35</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5002317162841093</v>
+        <v>0.500233194656849</v>
       </c>
       <c r="I29" t="n">
-        <v>175081.1006994382</v>
+        <v>175081.6181298972</v>
       </c>
       <c r="J29" t="n">
-        <v>1175081.100699438</v>
+        <v>1175081.618129897</v>
       </c>
       <c r="K29" t="n">
-        <v>70831.52798490437</v>
+        <v>70831.54084035222</v>
       </c>
       <c r="L29" t="n">
         <v>10.74285714285714</v>
       </c>
       <c r="M29" t="n">
-        <v>26.77582676415089</v>
+        <v>26.77579790057085</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F30" t="n">
-        <v>16.55007946241924</v>
+        <v>16.55002190378127</v>
       </c>
       <c r="G30" t="n">
         <v>28</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5910742665149729</v>
+        <v>0.591072210849331</v>
       </c>
       <c r="I30" t="n">
-        <v>165500.7946241924</v>
+        <v>165500.2190378127</v>
       </c>
       <c r="J30" t="n">
-        <v>1165500.794624192</v>
+        <v>1165500.219037813</v>
       </c>
       <c r="K30" t="n">
-        <v>59024.75572479467</v>
+        <v>59024.73107557</v>
       </c>
       <c r="L30" t="n">
         <v>9.357142857142858</v>
       </c>
       <c r="M30" t="n">
-        <v>30.08178128799766</v>
+        <v>30.08178730592843</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1901,28 +1901,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F31" t="n">
-        <v>13.44341137669126</v>
+        <v>13.44334594496093</v>
       </c>
       <c r="G31" t="n">
         <v>28</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4801218348818307</v>
+        <v>0.4801194980343189</v>
       </c>
       <c r="I31" t="n">
-        <v>134434.1137669126</v>
+        <v>134433.4594496093</v>
       </c>
       <c r="J31" t="n">
-        <v>1134434.113766913</v>
+        <v>1134433.459449609</v>
       </c>
       <c r="K31" t="n">
-        <v>58337.63986865056</v>
+        <v>58337.61268540047</v>
       </c>
       <c r="L31" t="n">
         <v>9.821428571428571</v>
       </c>
       <c r="M31" t="n">
-        <v>30.95747229363816</v>
+        <v>30.95748396157298</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F32" t="n">
-        <v>6.678532226397167</v>
+        <v>6.678539468839182</v>
       </c>
       <c r="G32" t="n">
         <v>28</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2385190080856131</v>
+        <v>0.2385192667442565</v>
       </c>
       <c r="I32" t="n">
-        <v>66785.32226397167</v>
+        <v>66785.39468839183</v>
       </c>
       <c r="J32" t="n">
-        <v>1066785.322263972</v>
+        <v>1066785.394688392</v>
       </c>
       <c r="K32" t="n">
-        <v>56623.50318413318</v>
+        <v>56623.49938463305</v>
       </c>
       <c r="L32" t="n">
         <v>9.75</v>
       </c>
       <c r="M32" t="n">
-        <v>34.931312811978</v>
+        <v>34.93129181640218</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>38.70967741935484</v>
       </c>
       <c r="F33" t="n">
-        <v>3.482734412665514</v>
+        <v>3.482793840312771</v>
       </c>
       <c r="G33" t="n">
         <v>31</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1123462713763069</v>
+        <v>0.1123481883971862</v>
       </c>
       <c r="I33" t="n">
-        <v>34827.34412665514</v>
+        <v>34827.93840312771</v>
       </c>
       <c r="J33" t="n">
-        <v>1034827.344126655</v>
+        <v>1034827.938403128</v>
       </c>
       <c r="K33" t="n">
-        <v>55034.59564065361</v>
+        <v>55034.61762786975</v>
       </c>
       <c r="L33" t="n">
         <v>12</v>
       </c>
       <c r="M33" t="n">
-        <v>32.20717873358061</v>
+        <v>32.20716020125495</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,28 +2045,28 @@
         <v>38.70967741935484</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7243792926472262</v>
+        <v>0.7244287836276809</v>
       </c>
       <c r="G34" t="n">
         <v>31</v>
       </c>
       <c r="H34" t="n">
-        <v>0.02336707395636214</v>
+        <v>0.02336867043960261</v>
       </c>
       <c r="I34" t="n">
-        <v>7243.792926472262</v>
+        <v>7244.28783627681</v>
       </c>
       <c r="J34" t="n">
-        <v>1007243.792926472</v>
+        <v>1007244.287836277</v>
       </c>
       <c r="K34" t="n">
-        <v>54465.62760160865</v>
+        <v>54465.64688709193</v>
       </c>
       <c r="L34" t="n">
         <v>12.41935483870968</v>
       </c>
       <c r="M34" t="n">
-        <v>33.05625019054274</v>
+        <v>33.05623744166106</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2093,28 +2093,28 @@
         <v>36</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2618697552753496</v>
+        <v>-0.2618713412689161</v>
       </c>
       <c r="G35" t="n">
         <v>25</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.01047479021101399</v>
+        <v>-0.01047485365075665</v>
       </c>
       <c r="I35" t="n">
-        <v>-2618.697552753496</v>
+        <v>-2618.713412689161</v>
       </c>
       <c r="J35" t="n">
-        <v>997381.3024472465</v>
+        <v>997381.2865873108</v>
       </c>
       <c r="K35" t="n">
-        <v>46411.74670743827</v>
+        <v>46411.73880969534</v>
       </c>
       <c r="L35" t="n">
         <v>9.92</v>
       </c>
       <c r="M35" t="n">
-        <v>30.51011804255807</v>
+        <v>30.51008085681374</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2141,28 +2141,28 @@
         <v>39.28571428571428</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.154327316729259</v>
+        <v>-1.154349339809653</v>
       </c>
       <c r="G36" t="n">
         <v>28</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.04122597559747353</v>
+        <v>-0.04122676213605903</v>
       </c>
       <c r="I36" t="n">
-        <v>-11543.27316729259</v>
+        <v>-11543.49339809653</v>
       </c>
       <c r="J36" t="n">
-        <v>988456.7268327074</v>
+        <v>988456.5066019035</v>
       </c>
       <c r="K36" t="n">
-        <v>52827.38811631487</v>
+        <v>52827.37061408847</v>
       </c>
       <c r="L36" t="n">
         <v>10.17857142857143</v>
       </c>
       <c r="M36" t="n">
-        <v>34.93131281197799</v>
+        <v>34.93129181640217</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.622879821638681</v>
+        <v>-1.622785370682308</v>
       </c>
       <c r="G37" t="n">
         <v>33</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.04917817641329337</v>
+        <v>-0.04917531426310024</v>
       </c>
       <c r="I37" t="n">
-        <v>-16228.79821638681</v>
+        <v>-16227.85370682308</v>
       </c>
       <c r="J37" t="n">
-        <v>983771.2017836132</v>
+        <v>983772.1462931769</v>
       </c>
       <c r="K37" t="n">
-        <v>58880.78614473325</v>
+        <v>58880.82541605231</v>
       </c>
       <c r="L37" t="n">
         <v>10.66666666666667</v>
       </c>
       <c r="M37" t="n">
-        <v>31.65078300280713</v>
+        <v>31.65075606084242</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2237,28 +2237,28 @@
         <v>34.61538461538461</v>
       </c>
       <c r="F38" t="n">
-        <v>-4.271218643738259</v>
+        <v>-4.27120220165666</v>
       </c>
       <c r="G38" t="n">
         <v>26</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1642776401437792</v>
+        <v>-0.1642770077560254</v>
       </c>
       <c r="I38" t="n">
-        <v>-42712.1864373826</v>
+        <v>-42712.0220165666</v>
       </c>
       <c r="J38" t="n">
-        <v>957287.8135626174</v>
+        <v>957287.9779834334</v>
       </c>
       <c r="K38" t="n">
-        <v>47714.19207922939</v>
+        <v>47714.19255910188</v>
       </c>
       <c r="L38" t="n">
         <v>9.423076923076923</v>
       </c>
       <c r="M38" t="n">
-        <v>30.99121406496133</v>
+        <v>30.99117713662023</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2285,28 +2285,28 @@
         <v>36</v>
       </c>
       <c r="F39" t="n">
-        <v>-4.544233371829346</v>
+        <v>-4.544264258186531</v>
       </c>
       <c r="G39" t="n">
         <v>25</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1817693348731738</v>
+        <v>-0.1817705703274612</v>
       </c>
       <c r="I39" t="n">
-        <v>-45442.33371829346</v>
+        <v>-45442.64258186531</v>
       </c>
       <c r="J39" t="n">
-        <v>954557.6662817065</v>
+        <v>954557.3574181347</v>
       </c>
       <c r="K39" t="n">
-        <v>44932.06087040354</v>
+        <v>44932.04330013024</v>
       </c>
       <c r="L39" t="n">
         <v>10.64</v>
       </c>
       <c r="M39" t="n">
-        <v>32.06555669781145</v>
+        <v>32.06553130543728</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>37.03703703703704</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.727014596117032</v>
+        <v>-6.727027662774711</v>
       </c>
       <c r="G40" t="n">
         <v>27</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.2491486887450753</v>
+        <v>-0.2491491726953597</v>
       </c>
       <c r="I40" t="n">
-        <v>-67270.14596117032</v>
+        <v>-67270.27662774711</v>
       </c>
       <c r="J40" t="n">
-        <v>932729.8540388297</v>
+        <v>932729.7233722529</v>
       </c>
       <c r="K40" t="n">
-        <v>49483.57190600705</v>
+        <v>49483.56404803752</v>
       </c>
       <c r="L40" t="n">
         <v>11.44444444444444</v>
       </c>
       <c r="M40" t="n">
-        <v>39.01207413000407</v>
+        <v>39.01206905739512</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>36</v>
       </c>
       <c r="F41" t="n">
-        <v>-7.088627894340677</v>
+        <v>-7.08866566212118</v>
       </c>
       <c r="G41" t="n">
         <v>25</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.2835451157736271</v>
+        <v>-0.2835466264848472</v>
       </c>
       <c r="I41" t="n">
-        <v>-70886.27894340677</v>
+        <v>-70886.65662121179</v>
       </c>
       <c r="J41" t="n">
-        <v>929113.7210565932</v>
+        <v>929113.3433787882</v>
       </c>
       <c r="K41" t="n">
-        <v>44404.20937707005</v>
+        <v>44404.1898591389</v>
       </c>
       <c r="L41" t="n">
         <v>11.16</v>
       </c>
       <c r="M41" t="n">
-        <v>32.91640190051838</v>
+        <v>32.91638238910438</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>34.61538461538461</v>
       </c>
       <c r="F42" t="n">
-        <v>-8.381436564720341</v>
+        <v>-8.381449016486714</v>
       </c>
       <c r="G42" t="n">
         <v>26</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.3223629447969362</v>
+        <v>-0.3223634237110274</v>
       </c>
       <c r="I42" t="n">
-        <v>-83814.36564720341</v>
+        <v>-83814.49016486714</v>
       </c>
       <c r="J42" t="n">
-        <v>916185.6343527966</v>
+        <v>916185.5098351329</v>
       </c>
       <c r="K42" t="n">
-        <v>46179.1633460391</v>
+        <v>46179.15348671275</v>
       </c>
       <c r="L42" t="n">
         <v>10.11538461538461</v>
       </c>
       <c r="M42" t="n">
-        <v>32.53588402513194</v>
+        <v>32.53585880851349</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,28 +2477,28 @@
         <v>37.03703703703704</v>
       </c>
       <c r="F43" t="n">
-        <v>-9.213226603447682</v>
+        <v>-9.213246850335237</v>
       </c>
       <c r="G43" t="n">
         <v>27</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.3412306149425067</v>
+        <v>-0.341231364827231</v>
       </c>
       <c r="I43" t="n">
-        <v>-92132.26603447681</v>
+        <v>-92132.46850335237</v>
       </c>
       <c r="J43" t="n">
-        <v>907867.7339655232</v>
+        <v>907867.5314966476</v>
       </c>
       <c r="K43" t="n">
-        <v>48943.57790762297</v>
+        <v>48943.56789871468</v>
       </c>
       <c r="L43" t="n">
         <v>11.92592592592593</v>
       </c>
       <c r="M43" t="n">
-        <v>39.77591764777173</v>
+        <v>39.77591763279856</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2525,28 +2525,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F44" t="n">
-        <v>-9.301108124243877</v>
+        <v>-9.301163324964907</v>
       </c>
       <c r="G44" t="n">
         <v>28</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3321824330087099</v>
+        <v>-0.3321844044630324</v>
       </c>
       <c r="I44" t="n">
-        <v>-93011.08124243875</v>
+        <v>-93011.63324964908</v>
       </c>
       <c r="J44" t="n">
-        <v>906988.9187575612</v>
+        <v>906988.3667503509</v>
       </c>
       <c r="K44" t="n">
-        <v>50156.5980749895</v>
+        <v>50156.56901101815</v>
       </c>
       <c r="L44" t="n">
         <v>10.92857142857143</v>
       </c>
       <c r="M44" t="n">
-        <v>39.01207413000407</v>
+        <v>39.01206905739512</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>34.61538461538461</v>
       </c>
       <c r="F45" t="n">
-        <v>-10.82354958941716</v>
+        <v>-10.82356910426682</v>
       </c>
       <c r="G45" t="n">
         <v>26</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.416290368823737</v>
+        <v>-0.4162911193948776</v>
       </c>
       <c r="I45" t="n">
-        <v>-108235.4958941716</v>
+        <v>-108235.6910426682</v>
       </c>
       <c r="J45" t="n">
-        <v>891764.5041058284</v>
+        <v>891764.3089573318</v>
       </c>
       <c r="K45" t="n">
-        <v>45617.73772006088</v>
+        <v>45617.72571948095</v>
       </c>
       <c r="L45" t="n">
         <v>10.61538461538461</v>
       </c>
       <c r="M45" t="n">
-        <v>33.38083861137537</v>
+        <v>33.38081923500231</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F46" t="n">
-        <v>-11.71870710058915</v>
+        <v>-11.71876815067587</v>
       </c>
       <c r="G46" t="n">
         <v>28</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4185252535924698</v>
+        <v>-0.4185274339527095</v>
       </c>
       <c r="I46" t="n">
-        <v>-117187.0710058915</v>
+        <v>-117187.6815067587</v>
       </c>
       <c r="J46" t="n">
-        <v>882812.9289941085</v>
+        <v>882812.3184932413</v>
       </c>
       <c r="K46" t="n">
-        <v>49631.50651647533</v>
+        <v>49631.47560694496</v>
       </c>
       <c r="L46" t="n">
         <v>11.39285714285714</v>
       </c>
       <c r="M46" t="n">
-        <v>39.77591764777175</v>
+        <v>39.77591763279855</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
